--- a/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4705" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4821" uniqueCount="1126">
   <si>
     <t>Notes</t>
   </si>
@@ -3240,6 +3240,180 @@
   </si>
   <si>
     <t>Wed Jul 08 07:39:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:53:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:02:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:21:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:22:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:24:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:26:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:30:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:33:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:34:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 08:50:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 09:00:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 09:13:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 09:24:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 09:37:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 09:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 10:02:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 10:11:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 10:24:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 10:37:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 10:49:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 10:55:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 11:11:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 11:23:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 11:34:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 11:47:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 11:57:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 12:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:46:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:49:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:50:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:51:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:53:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:54:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:56:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:57:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:59:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:00:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:02:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:03:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:07:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:09:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:11:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:12:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:14:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:15:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:17:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:18:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:20:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:22:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:24:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:25:48 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3705,7 +3879,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1059</v>
+        <v>1117</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -4809,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1064</v>
+        <v>1122</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -4905,7 +5079,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1065</v>
+        <v>1123</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>103</v>
@@ -5001,7 +5175,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1066</v>
+        <v>1124</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>103</v>
@@ -5097,7 +5271,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1067</v>
+        <v>1125</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>103</v>
@@ -5315,7 +5489,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1060</v>
+        <v>1118</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -5411,7 +5585,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1061</v>
+        <v>1119</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>103</v>
@@ -5507,7 +5681,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1062</v>
+        <v>1120</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>103</v>
@@ -5603,7 +5777,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1063</v>
+        <v>1121</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>103</v>
@@ -5819,7 +5993,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1047</v>
+        <v>1105</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -5915,7 +6089,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1048</v>
+        <v>1106</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>103</v>
@@ -6011,7 +6185,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1049</v>
+        <v>1107</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>103</v>
@@ -6107,7 +6281,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1050</v>
+        <v>1108</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>103</v>
@@ -6323,7 +6497,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1055</v>
+        <v>1113</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -6425,7 +6599,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1056</v>
+        <v>1114</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>103</v>
@@ -6524,7 +6698,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1057</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>103</v>
@@ -6623,7 +6797,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1058</v>
+        <v>1116</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>103</v>
@@ -6842,7 +7016,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1051</v>
+        <v>1109</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -6938,7 +7112,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1052</v>
+        <v>1110</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>103</v>
@@ -7034,7 +7208,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1053</v>
+        <v>1111</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>103</v>
@@ -7130,7 +7304,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1054</v>
+        <v>1112</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>103</v>
@@ -7340,7 +7514,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1044</v>
+        <v>1102</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -7555,7 +7729,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1046</v>
+        <v>1104</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
@@ -7767,7 +7941,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1045</v>
+        <v>1103</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>103</v>
